--- a/cupia-ai-research/docs/reference/05_견적서_표준양식_씨커스.xlsx
+++ b/cupia-ai-research/docs/reference/05_견적서_표준양식_씨커스.xlsx
@@ -14,7 +14,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'견적서(인력)'!$A$1:$L$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'견적서(업무)'!$A$1:$K$30</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
@@ -7059,18 +7059,18 @@
   <mergeCells count="17">
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B17:B19"/>
+    <mergeCell ref="H25:H26"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="I25:I26"/>
     <mergeCell ref="F25:F26"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B1:J1"/>
-    <mergeCell ref="G25:G26"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B25:E26"/>
     <mergeCell ref="B27:J28"/>
-    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="G25:G26"/>
     <mergeCell ref="B4:F5"/>
     <mergeCell ref="B16:J16"/>
     <mergeCell ref="C17:D19"/>
